--- a/reports/pdf_weekly_20260807.xlsx
+++ b/reports/pdf_weekly_20260807.xlsx
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1247353800</v>
+        <v>466342800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.76%→1.00%</t>
+          <t>1.03%→1.16%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>53→75</t>
+          <t>211→233</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>466342800</v>
+        <v>1247353800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.16%</t>
+          <t>0.76%→1.00%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>211→233</t>
+          <t>53→75</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1986,23 +1986,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>44212500</v>
+        <v>31893750</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.20%</t>
+          <t>2.56%→2.67%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2030,23 +2030,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>31893750</v>
+        <v>44212500</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.56%→2.67%</t>
+          <t>1.03%→1.20%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">

--- a/reports/pdf_weekly_20260807.xlsx
+++ b/reports/pdf_weekly_20260807.xlsx
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>466342800</v>
+        <v>1247353800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.16%</t>
+          <t>0.76%→1.00%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>211→233</t>
+          <t>53→75</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1247353800</v>
+        <v>466342800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.76%→1.00%</t>
+          <t>1.03%→1.16%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>53→75</t>
+          <t>211→233</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2118,23 +2118,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>41670000</v>
+        <v>26055000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.59%</t>
+          <t>0.91%→1.00%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2162,23 +2162,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>54540000</v>
+        <v>41670000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.92%</t>
+          <t>2.43%→2.59%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G51" s="17" t="n"/>
@@ -2190,23 +2190,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>26055000</v>
+        <v>54540000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.00%</t>
+          <t>2.72%→2.92%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G52" s="17" t="n"/>

--- a/reports/pdf_weekly_20260807.xlsx
+++ b/reports/pdf_weekly_20260807.xlsx
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1247353800</v>
+        <v>466342800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.76%→1.00%</t>
+          <t>1.03%→1.16%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>53→75</t>
+          <t>211→233</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>466342800</v>
+        <v>1247353800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.16%</t>
+          <t>0.76%→1.00%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>211→233</t>
+          <t>53→75</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1986,23 +1986,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>31893750</v>
+        <v>44212500</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.56%→2.67%</t>
+          <t>1.03%→1.20%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2030,23 +2030,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>44212500</v>
+        <v>31893750</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.20%</t>
+          <t>2.56%→2.67%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2162,23 +2162,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>41670000</v>
+        <v>54540000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.59%</t>
+          <t>2.72%→2.92%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G51" s="17" t="n"/>
@@ -2190,23 +2190,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>54540000</v>
+        <v>41670000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.92%</t>
+          <t>2.43%→2.59%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G52" s="17" t="n"/>

--- a/reports/pdf_weekly_20260807.xlsx
+++ b/reports/pdf_weekly_20260807.xlsx
@@ -2118,23 +2118,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>26055000</v>
+        <v>54540000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.00%</t>
+          <t>2.72%→2.92%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2162,23 +2162,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>54540000</v>
+        <v>26055000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.92%</t>
+          <t>0.91%→1.00%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G51" s="17" t="n"/>
